--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T05:44:49+00:00</t>
+    <t>2024-12-17T07:37:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T07:37:54+00:00</t>
+    <t>2024-12-17T09:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T09:20:51+00:00</t>
+    <t>2024-12-17T09:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T09:54:20+00:00</t>
+    <t>2024-12-17T09:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
